--- a/testdata/realdata/devices.xlsx
+++ b/testdata/realdata/devices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,10 +469,15 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>服务客户</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>经度</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>纬度</t>
         </is>
@@ -531,10 +536,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>126.62762</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>45.75936</t>
         </is>
@@ -593,10 +603,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>126.62762</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>45.75936</t>
         </is>
@@ -655,10 +670,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>125.10148</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>46.5969</t>
         </is>
@@ -717,10 +737,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>125.10148</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>46.5969</t>
         </is>
@@ -779,10 +804,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>123.94954</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>47.33924</t>
         </is>
@@ -841,10 +871,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>123.94954</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>47.33924</t>
         </is>
@@ -891,7 +926,11 @@
           <t>MR1727803072</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -899,10 +938,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>125.11985</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>48.45402</t>
         </is>
@@ -949,7 +993,11 @@
           <t>MR1727803072</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -957,10 +1005,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>125.11985</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>48.45402</t>
         </is>
@@ -1007,7 +1060,11 @@
           <t>MR469656125</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1015,10 +1072,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>125.23123</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>49.17348</t>
         </is>
@@ -1065,7 +1127,11 @@
           <t>MR469656125</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1073,10 +1139,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>125.23123</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>49.17348</t>
         </is>
@@ -1123,7 +1194,11 @@
           <t>MR678337697</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1131,10 +1206,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>124.13165</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>50.40579</t>
         </is>
@@ -1181,7 +1261,11 @@
           <t>MR678337697</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1189,10 +1273,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>124.13165</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>50.40579</t>
         </is>
@@ -1239,7 +1328,11 @@
           <t>MR962010355</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1247,10 +1340,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>124.70199</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>52.33318</t>
         </is>
@@ -1297,7 +1395,11 @@
           <t>MR962010355</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1305,10 +1407,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>124.70199</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>52.33318</t>
         </is>
@@ -1355,7 +1462,11 @@
           <t>MR280162986</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1363,10 +1474,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>CUST-011</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>122.533</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>52.97144</t>
         </is>
@@ -1413,7 +1529,11 @@
           <t>MR280162986</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>IGP-OSPF-01</t>
@@ -1421,10 +1541,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>CUST-011</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>122.533</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>52.97144</t>
         </is>
@@ -1471,7 +1596,11 @@
           <t>MR4059698545</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1479,10 +1608,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>129.61138</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>44.57902</t>
         </is>
@@ -1529,7 +1663,11 @@
           <t>MR4059698545</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1537,10 +1675,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>129.61138</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>44.57902</t>
         </is>
@@ -1587,7 +1730,11 @@
           <t>MR304758391</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1595,10 +1742,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>130.37472</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>46.80374</t>
         </is>
@@ -1645,7 +1797,11 @@
           <t>MR304758391</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1653,10 +1809,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>130.37472</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>46.80374</t>
         </is>
@@ -1703,7 +1864,11 @@
           <t>MR6359892789</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1711,10 +1876,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>128.31581</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>44.9802</t>
         </is>
@@ -1761,7 +1931,11 @@
           <t>MR6359892789</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1769,10 +1943,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>128.31581</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>44.9802</t>
         </is>
@@ -1819,7 +1998,11 @@
           <t>MR244081815</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1827,10 +2010,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>126.96272</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>46.65104</t>
         </is>
@@ -1877,7 +2065,11 @@
           <t>MR244081815</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1885,10 +2077,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>126.96272</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>46.65104</t>
         </is>
@@ -1935,7 +2132,11 @@
           <t>MR244082251</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -1943,10 +2144,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>128.83376</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>47.72537</t>
         </is>
@@ -1993,7 +2199,11 @@
           <t>MR244082251</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -2001,10 +2211,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>128.83376</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>47.72537</t>
         </is>
@@ -2051,7 +2266,11 @@
           <t>MR244081526</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -2059,10 +2278,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>131.00666</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>45.77036</t>
         </is>
@@ -2109,7 +2333,11 @@
           <t>MR244081526</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -2117,10 +2345,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>131.00666</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>45.77036</t>
         </is>
@@ -2167,7 +2400,11 @@
           <t>MR502220401</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -2175,10 +2412,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>130.96193</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>45.29285</t>
         </is>
@@ -2225,7 +2467,11 @@
           <t>MR502220401</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
@@ -2233,10 +2479,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>130.96193</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>45.29285</t>
         </is>

--- a/testdata/realdata/devices.xlsx
+++ b/testdata/realdata/devices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEV-279116876-01</t>
+          <t>DEV-1603990225-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>哈尔滨市传输设备01</t>
+          <t>穆棱镇传输设备01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>哈尔滨</t>
+          <t>牡丹江</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,49 +521,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MR279116876</t>
+          <t>MR1603990225</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-005</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>126.62762</t>
+          <t>130.25502</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>45.75936</t>
+          <t>44.52703</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEV-279116876-02</t>
+          <t>DEV-1603990225-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>哈尔滨市传输设备02</t>
+          <t>穆棱镇传输设备02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>哈尔滨</t>
+          <t>牡丹江</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -588,49 +588,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MR279116876</t>
+          <t>MR1603990225</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>126.62762</t>
+          <t>130.25502</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>45.75936</t>
+          <t>44.52703</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEV-244077958-01</t>
+          <t>DEV-1727803072-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大庆市传输设备01</t>
+          <t>讷河市传输设备01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>大庆</t>
+          <t>齐齐哈尔</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MR244077958</t>
+          <t>MR1727803072</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -670,34 +670,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CUST-004</t>
+          <t>CUST-003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>125.10148</t>
+          <t>125.11985</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>46.5969</t>
+          <t>48.45402</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEV-244077958-02</t>
+          <t>DEV-1933473774-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>大庆市传输设备02</t>
+          <t>黑河市传输设备01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>大庆</t>
+          <t>黑河</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.41.0.12</t>
+          <t>10.42.0.11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -722,64 +722,64 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MR244077958</t>
+          <t>MR1933473774</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CUST-004</t>
+          <t>CUST-009</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>125.10148</t>
+          <t>127.49469</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>46.5969</t>
+          <t>50.23222</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEV-244081515-01</t>
+          <t>DEV-1933473774-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>齐齐哈尔市传输设备01</t>
+          <t>黑河市传输设备02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>齐齐哈尔</t>
+          <t>黑河</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OptiX OSN 9800</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10.42.0.11</t>
+          <t>10.42.0.12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -789,64 +789,64 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MR244081515</t>
+          <t>MR1933473774</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CUST-003</t>
+          <t>CUST-009</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>123.94954</t>
+          <t>127.49469</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>47.33924</t>
+          <t>50.23222</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-244081515-02</t>
+          <t>DEV-1933473774-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>齐齐哈尔市传输设备02</t>
+          <t>黑河市传输设备03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>齐齐哈尔</t>
+          <t>黑河</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10.42.0.12</t>
+          <t>10.42.0.13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -856,49 +856,49 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MR244081515</t>
+          <t>MR1933473774</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CUST-003</t>
+          <t>CUST-009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>123.94954</t>
+          <t>127.49469</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>47.33924</t>
+          <t>50.23222</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEV-1727803072-01</t>
+          <t>DEV-2168737545-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>讷河市传输设备01</t>
+          <t>大同区传输设备01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>齐齐哈尔</t>
+          <t>大庆</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MR1727803072</t>
+          <t>MR2168737545</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -938,34 +938,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>125.11985</t>
+          <t>124.69792</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>48.45402</t>
+          <t>46.09946</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEV-1727803072-02</t>
+          <t>DEV-2168737545-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>讷河市传输设备02</t>
+          <t>大同区传输设备02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>齐齐哈尔</t>
+          <t>大庆</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MR1727803072</t>
+          <t>MR2168737545</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1005,34 +1005,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-004</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>125.11985</t>
+          <t>124.69792</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>48.45402</t>
+          <t>46.09946</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEV-469656125-01</t>
+          <t>DEV-2289935762-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>嫩江市传输设备01</t>
+          <t>周家街道传输设备01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MR469656125</t>
+          <t>MR2289935762</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1077,29 +1077,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>125.23123</t>
+          <t>126.65297</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>49.17348</t>
+          <t>45.46102</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEV-469656125-02</t>
+          <t>DEV-244076868-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>嫩江市传输设备02</t>
+          <t>巴彦县传输设备01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>绥化</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.44.0.12</t>
+          <t>10.45.0.11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1124,64 +1124,64 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MR469656125</t>
+          <t>MR244076868</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-007</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>125.23123</t>
+          <t>127.35885</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>49.17348</t>
+          <t>46.31724</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DEV-678337697-01</t>
+          <t>DEV-244076933-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>加格达奇区传输设备01</t>
+          <t>宾县传输设备01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OptiX OSN 9800</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10.45.0.11</t>
+          <t>10.46.0.11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1191,64 +1191,64 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MR678337697</t>
+          <t>MR244076933</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CUST-010</t>
+          <t>CUST-001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>124.13165</t>
+          <t>127.46029</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>50.40579</t>
+          <t>45.74342</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DEV-678337697-02</t>
+          <t>DEV-244076933-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>加格达奇区传输设备02</t>
+          <t>宾县传输设备02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10.45.0.12</t>
+          <t>10.46.0.12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1258,64 +1258,64 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MR678337697</t>
+          <t>MR244076933</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CUST-010</t>
+          <t>CUST-001</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>124.13165</t>
+          <t>127.46029</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>50.40579</t>
+          <t>45.74342</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEV-962010355-01</t>
+          <t>DEV-244077958-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>塔河县传输设备01</t>
+          <t>大庆市传输设备01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>大庆</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>10.46.0.11</t>
+          <t>10.47.0.11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MR962010355</t>
+          <t>MR244077958</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1340,49 +1340,49 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-004</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>124.70199</t>
+          <t>125.10148</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>52.33318</t>
+          <t>46.5969</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEV-962010355-02</t>
+          <t>DEV-244077958-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>塔河县传输设备02</t>
+          <t>大庆市传输设备02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>大庆</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>烽火</t>
+          <t>华为</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CiTRANS 660</t>
+          <t>OptiX OSN 9800</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>10.46.0.12</t>
+          <t>10.47.0.12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MR962010355</t>
+          <t>MR244077958</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,49 +1407,49 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-004</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>124.70199</t>
+          <t>125.10148</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>52.33318</t>
+          <t>46.5969</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEV-280162986-01</t>
+          <t>DEV-244077958-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>漠河市传输设备01</t>
+          <t>大庆市传输设备03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>大庆</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>烽火</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CiTRANS 660</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.47.0.11</t>
+          <t>10.47.0.13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MR280162986</t>
+          <t>MR244077958</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1474,34 +1474,34 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CUST-011</t>
+          <t>CUST-004</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>122.533</t>
+          <t>125.10148</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>52.97144</t>
+          <t>46.5969</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DEV-280162986-02</t>
+          <t>DEV-244079035-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>漠河市传输设备02</t>
+          <t>方正县传输设备01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加格达奇</t>
+          <t>牡丹江</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.47.0.12</t>
+          <t>10.48.0.11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1526,64 +1526,64 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MR280162986</t>
+          <t>MR244079035</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RING-HDQ</t>
+          <t>RING-JM</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>IGP-OSPF-01</t>
+          <t>IGP-ISIS-02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CUST-011</t>
+          <t>CUST-005</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>122.533</t>
+          <t>128.92725</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>52.97144</t>
+          <t>45.78637</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEV-4059698545-01</t>
+          <t>DEV-244079624-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>牡丹江市传输设备01</t>
+          <t>甘南县传输设备01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>牡丹江</t>
+          <t>齐齐哈尔</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OptiX OSN 9800</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10.48.0.11</t>
+          <t>10.49.0.11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1593,64 +1593,64 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MR4059698545</t>
+          <t>MR244079624</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>RING-JM</t>
+          <t>RING-HDQ</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>IGP-ISIS-02</t>
+          <t>IGP-OSPF-01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>CUST-005</t>
+          <t>CUST-003</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>129.61138</t>
+          <t>123.85974</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>44.57902</t>
+          <t>47.98002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DEV-4059698545-02</t>
+          <t>DEV-244079624-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>牡丹江市传输设备02</t>
+          <t>甘南县传输设备02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>牡丹江</t>
+          <t>齐齐哈尔</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.48.0.12</t>
+          <t>10.49.0.12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1660,64 +1660,64 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MR4059698545</t>
+          <t>MR244079624</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>RING-JM</t>
+          <t>RING-HDQ</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>IGP-ISIS-02</t>
+          <t>IGP-OSPF-01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CUST-005</t>
+          <t>CUST-003</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>129.61138</t>
+          <t>123.85974</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>44.57902</t>
+          <t>47.98002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DEV-304758391-01</t>
+          <t>DEV-244080476-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>佳木斯市传输设备01</t>
+          <t>鹤岗市传输设备01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>佳木斯</t>
+          <t>鹤岗</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10.49.0.11</t>
+          <t>10.50.0.11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MR304758391</t>
+          <t>MR244080476</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1742,49 +1742,49 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CUST-006</t>
+          <t>CUST-009</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>130.37472</t>
+          <t>130.26848</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>46.80374</t>
+          <t>47.32723</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DEV-304758391-02</t>
+          <t>DEV-244080476-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>佳木斯市传输设备02</t>
+          <t>鹤岗市传输设备02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>佳木斯</t>
+          <t>鹤岗</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>烽火</t>
+          <t>华为</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CiTRANS 660</t>
+          <t>OptiX OSN 9800</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.49.0.12</t>
+          <t>10.50.0.12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MR304758391</t>
+          <t>MR244080476</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1809,49 +1809,49 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>CUST-006</t>
+          <t>CUST-009</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>130.37472</t>
+          <t>130.26848</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>46.80374</t>
+          <t>47.32723</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DEV-6359892789-01</t>
+          <t>DEV-244080476-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>尚志市传输设备01</t>
+          <t>鹤岗市传输设备03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>牡丹江</t>
+          <t>鹤岗</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>烽火</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CiTRANS 660</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.50.0.11</t>
+          <t>10.50.0.13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MR6359892789</t>
+          <t>MR244080476</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1876,34 +1876,34 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-009</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>128.31581</t>
+          <t>130.26848</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>44.9802</t>
+          <t>47.32723</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DEV-6359892789-02</t>
+          <t>DEV-244080682-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>尚志市传输设备02</t>
+          <t>呼兰区传输设备01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>牡丹江</t>
+          <t>哈尔滨</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.50.0.12</t>
+          <t>10.51.0.11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MR6359892789</t>
+          <t>MR244080682</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>RING-JM</t>
+          <t>RING-HDQ</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>IGP-ISIS-02</t>
+          <t>IGP-OSPF-01</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1948,44 +1948,44 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>128.31581</t>
+          <t>126.82563</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>44.9802</t>
+          <t>46.14398</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEV-244081815-01</t>
+          <t>DEV-244080693-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>绥化市传输设备01</t>
+          <t>桦南县传输设备01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>绥化</t>
+          <t>七台河</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OptiX OSN 9800</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10.51.0.11</t>
+          <t>10.52.0.11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MR244081815</t>
+          <t>MR244080693</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2010,49 +2010,49 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CUST-007</t>
+          <t>CUST-012</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>126.96272</t>
+          <t>130.55706</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>46.65104</t>
+          <t>46.23543</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEV-244081815-02</t>
+          <t>DEV-244080693-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>绥化市传输设备02</t>
+          <t>桦南县传输设备02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>绥化</t>
+          <t>七台河</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10.51.0.12</t>
+          <t>10.52.0.12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MR244081815</t>
+          <t>MR244080693</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2077,49 +2077,49 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>CUST-007</t>
+          <t>CUST-012</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>126.96272</t>
+          <t>130.55706</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>46.65104</t>
+          <t>46.23543</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEV-244082251-01</t>
+          <t>DEV-244081168-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>伊春市传输设备01</t>
+          <t>林口县传输设备01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>伊春</t>
+          <t>鸡西</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>中兴</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ZXMP M920</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10.52.0.11</t>
+          <t>10.53.0.11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MR244082251</t>
+          <t>MR244081168</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2144,49 +2144,49 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CUST-008</t>
+          <t>CUST-005</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>128.83376</t>
+          <t>130.09047</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>47.72537</t>
+          <t>45.44278</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DEV-244082251-02</t>
+          <t>DEV-244081218-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>伊春市传输设备02</t>
+          <t>漠河市传输设备01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>伊春</t>
+          <t>加格达奇</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>烽火</t>
+          <t>华为</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CiTRANS 660</t>
+          <t>OptiX OSN 9800</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.52.0.12</t>
+          <t>10.54.0.11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2196,64 +2196,64 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MR244082251</t>
+          <t>MR244081218</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RING-JM</t>
+          <t>RING-HDQ</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IGP-ISIS-02</t>
+          <t>IGP-OSPF-01</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CUST-008</t>
+          <t>CUST-010</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>128.83376</t>
+          <t>122.79333</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>47.72537</t>
+          <t>52.97592</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DEV-244081526-01</t>
+          <t>DEV-244081226-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>七台河市传输设备01</t>
+          <t>木兰县传输设备01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>七台河</t>
+          <t>绥化</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>烽火</t>
+          <t>中兴</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CiTRANS 660</t>
+          <t>ZXMP M920</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.53.0.11</t>
+          <t>10.55.0.11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MR244081526</t>
+          <t>MR244081226</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2278,49 +2278,49 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-007</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>131.00666</t>
+          <t>127.95504</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>45.77036</t>
+          <t>46.25763</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DEV-244081526-02</t>
+          <t>DEV-244081226-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>七台河市传输设备02</t>
+          <t>木兰县传输设备02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>七台河</t>
+          <t>绥化</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OptiX OSN 9800</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10.53.0.12</t>
+          <t>10.55.0.12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MR244081526</t>
+          <t>MR244081226</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2345,49 +2345,49 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>131.00666</t>
+          <t>127.95504</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>45.77036</t>
+          <t>46.25763</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEV-502220401-01</t>
+          <t>DEV-244081487-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>鸡西市传输设备01</t>
+          <t>青冈县传输设备01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>鸡西</t>
+          <t>大庆</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>华为</t>
+          <t>烽火</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OptiX OSN 9800</t>
+          <t>CiTRANS 660</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10.54.0.11</t>
+          <t>10.56.0.11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2397,99 +2397,7000 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MR502220401</t>
+          <t>MR244081487</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>RING-JM</t>
+          <t>RING-HDQ</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>IGP-ISIS-02</t>
+          <t>IGP-OSPF-01</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>CUST-001</t>
+          <t>CUST-004</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>130.96193</t>
+          <t>125.97445</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>45.29285</t>
+          <t>46.82543</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>DEV-244081508-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>庆安县传输设备01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10.57.0.11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>MR244081508</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>127.64522</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>47.06173</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DEV-244081515-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>齐齐哈尔市传输设备01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10.58.0.11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MR244081515</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>123.94954</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>47.33924</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEV-244081515-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>齐齐哈尔市传输设备02</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10.58.0.12</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MR244081515</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>123.94954</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>47.33924</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEV-244081515-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>齐齐哈尔市传输设备03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10.58.0.13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>MR244081515</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>123.94954</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>47.33924</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEV-244081526-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>七台河市传输设备01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>七台河</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10.59.0.11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MR244081526</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>131.00666</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>45.77036</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DEV-244081526-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>七台河市传输设备02</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>七台河</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10.59.0.12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>MR244081526</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>131.00666</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>45.77036</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DEV-244081526-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>七台河市传输设备03</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>七台河</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10.59.0.13</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MR244081526</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>131.00666</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>45.77036</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DEV-244081804-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>汤原县传输设备01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10.60.0.11</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>MR244081804</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>130.11379</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>47.00537</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DEV-244081815-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>绥化市传输设备01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10.61.0.11</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>MR244081815</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>126.96272</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>46.65104</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DEV-244081815-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>绥化市传输设备02</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10.61.0.12</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>MR244081815</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>126.96272</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>46.65104</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DEV-244081815-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>绥化市传输设备03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10.61.0.13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>MR244081815</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>126.96272</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>46.65104</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DEV-244081820-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>绥棱县传输设备01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10.62.0.11</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>MR244081820</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>127.71418</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>47.56538</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DEV-244081838-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>塔河县传输设备01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10.63.0.11</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>MR244081838</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>124.66072</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>52.71615</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DEV-244081998-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>望奎县传输设备01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10.64.0.11</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MR244081998</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>126.64513</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>46.8717</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DEV-244081998-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>望奎县传输设备02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10.64.0.12</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>MR244081998</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>126.64513</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>46.8717</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DEV-244082051-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>通河县传输设备01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10.65.0.11</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>MR244082051</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>128.78689</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>46.23863</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DEV-244082251-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>伊春市传输设备01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10.66.0.11</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>MR244082251</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>128.83376</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>47.72537</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DEV-244082251-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>伊春市传输设备02</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10.66.0.12</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>MR244082251</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>128.83376</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>47.72537</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DEV-244082251-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>伊春市传输设备03</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10.66.0.13</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>MR244082251</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>128.83376</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>47.72537</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DEV-244082264-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>延寿县传输设备01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10.67.0.11</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>MR244082264</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>128.45369</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>45.49308</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DEV-244082264-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>延寿县传输设备02</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10.67.0.12</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MR244082264</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>128.45369</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>45.49308</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DEV-244082302-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>依兰县传输设备01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>10.68.0.11</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>MR244082302</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>129.56504</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>46.32081</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DEV-244083414-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>鄂伦春自治旗传输设备01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10.69.0.11</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>MR244083414</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>123.84964</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>50.26411</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DEV-244083759-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>城子河区传输设备01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10.70.0.11</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>MR244083759</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>131.01943</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>45.3772</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DEV-244083759-02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>城子河区传输设备02</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10.70.0.12</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>MR244083759</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>131.01943</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>45.3772</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DEV-244083846-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>爱民区传输设备01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>10.71.0.11</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>MR244083846</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>129.513</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>44.70859</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DEV-244084005-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>道里区传输设备01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10.72.0.11</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>MR244084005</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>126.383</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>45.67747</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DEV-244084006-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>松北区传输设备01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10.73.0.11</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>MR244084006</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>126.44317</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>45.92371</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DEV-244084006-02</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>松北区传输设备02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10.73.0.12</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>MR244084006</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>126.44317</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>45.92371</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DEV-244084008-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>香坊区传输设备01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>10.74.0.11</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>MR244084008</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>126.75826</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>45.68864</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DEV-244084009-01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>南岗区传输设备01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>10.75.0.11</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>MR244084009</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>126.59196</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>45.69917</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DEV-244084010-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>道外区传输设备01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10.76.0.11</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>MR244084010</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>126.84886</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>45.83242</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DEV-244084010-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>道外区传输设备02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>10.76.0.12</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>MR244084010</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>126.84886</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>45.83242</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DEV-244084021-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>西安区传输设备01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10.77.0.11</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>MR244084021</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>129.50931</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>44.48814</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DEV-244084024-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>东安区传输设备01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10.78.0.11</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>MR244084024</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>129.79781</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>44.41053</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DEV-244084032-01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>乌翠区传输设备01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10.79.0.11</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>MR244084032</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>128.47359</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>47.661</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DEV-244084032-02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>乌翠区传输设备02</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>10.79.0.12</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>MR244084032</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>128.47359</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>47.661</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DEV-244084349-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>龙沙区传输设备01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10.80.0.11</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>MR244084349</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>123.91639</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>47.27764</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DEV-244084365-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>新兴区传输设备01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>七台河</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10.81.0.11</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>MR244084365</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>131.20039</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>46.01144</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DEV-279116876-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>哈尔滨市传输设备01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10.82.0.11</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MR279116876</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>126.62762</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>45.75936</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DEV-279116876-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>哈尔滨市传输设备02</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>10.82.0.12</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>MR279116876</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>126.62762</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>45.75936</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DEV-279116876-03</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>哈尔滨市传输设备03</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10.82.0.13</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MR279116876</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>126.62762</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>45.75936</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DEV-280162986-01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>漠河市-2传输设备01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>10.83.0.11</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>MR280162986</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>122.533</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>52.97144</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DEV-304758391-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>佳木斯市传输设备01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10.84.0.11</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>MR304758391</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>130.37472</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>46.80374</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DEV-304758391-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>佳木斯市传输设备02</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10.84.0.12</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>MR304758391</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>130.37472</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>46.80374</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DEV-304758391-03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>佳木斯市传输设备03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>10.84.0.13</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>MR304758391</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>130.37472</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>46.80374</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DEV-3364291968-01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>富裕县传输设备01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>10.85.0.11</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MR3364291968</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>124.56451</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>47.65992</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DEV-3364291968-02</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>富裕县传输设备02</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10.85.0.12</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>MR3364291968</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>124.56451</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>47.65992</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DEV-3373092558-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>安达市传输设备01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>10.86.0.11</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>MR3373092558</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>125.32856</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>46.41143</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DEV-3373116121-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>依安县传输设备01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>10.87.0.11</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>MR3373116121</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>125.31187</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>47.67951</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DEV-3768594801-01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>铁力市传输设备01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>10.88.0.11</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>MR3768594801</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>128.5499</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>46.8564</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DEV-3768594801-02</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>铁力市传输设备02</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>10.88.0.12</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>MR3768594801</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>128.5499</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>46.8564</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DEV-3826287683-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>巨源镇传输设备01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>10.89.0.11</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>MR3826287683</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>126.97</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>45.9408</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DEV-3826497558-01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>宾西镇传输设备01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>10.90.0.11</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>MR3826497558</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>127.15871</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>45.75203</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DEV-3826497583-01</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>永源镇传输设备01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>10.91.0.11</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>MR3826497583</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>127.00728</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>45.77498</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DEV-3826497583-02</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>永源镇传输设备02</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>10.91.0.12</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>MR3826497583</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>127.00728</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>45.77498</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-01</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>牡丹江市传输设备01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>10.92.0.11</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>MR4059698545</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>129.61138</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>44.57902</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-02</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>牡丹江市传输设备02</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>10.92.0.12</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>MR4059698545</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>129.61138</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>44.57902</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DEV-4059698545-03</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>牡丹江市传输设备03</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10.92.0.13</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>MR4059698545</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>129.61138</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>44.57902</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DEV-412234770-01</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>阿城区传输设备01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>10.93.0.11</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>MR412234770</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>127.1604</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>45.47508</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DEV-4417654189-01</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>伊春区传输设备01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>10.94.0.11</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>MR4417654189</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>128.88471</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>47.73947</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DEV-4417654189-02</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>伊春区传输设备02</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>伊春</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10.94.0.12</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>MR4417654189</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>128.88471</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>47.73947</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DEV-469656125-01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>嫩江市传输设备01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>10.95.0.11</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>MR469656125</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>125.23123</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>49.17348</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DEV-502220401-01</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>鸡西市传输设备01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>10.96.0.11</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>MR502220401</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>130.96193</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>45.29285</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>DEV-502220401-02</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>鸡西市传输设备02</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>鸡西</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>中兴</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>ZXMP M920</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>10.54.0.12</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>在网</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>10.96.0.12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>MR502220401</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>RING-JM</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>IGP-ISIS-02</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>130.96193</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>45.29285</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DEV-502220401-03</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>鸡西市传输设备03</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>10.96.0.13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>MR502220401</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>130.96193</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>45.29285</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DEV-5329377920-01</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>立新街道传输设备01</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10.97.0.11</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>MR5329377920</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>130.92655</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>45.23849</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DEV-5329377920-02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>立新街道传输设备02</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>10.97.0.12</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>MR5329377920</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>130.92655</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>45.23849</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-01</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>双鸭山市传输设备01</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>双鸭山</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>10.98.0.11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>MR5617724009</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>131.13312</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>46.67382</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-02</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>双鸭山市传输设备02</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>双鸭山</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>10.98.0.12</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>MR5617724009</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>131.13312</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>46.67382</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DEV-5617724009-03</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>双鸭山市传输设备03</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>双鸭山</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>10.98.0.13</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>MR5617724009</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>131.13312</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>46.67382</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DEV-6330273967-01</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>安达市-2传输设备01</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>10.99.0.11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>MR6330273967</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>125.41929</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>46.51698</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DEV-6331568977-01</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>肇东市传输设备01</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>10.100.0.11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>MR6331568977</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>CUST-001</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>130.96193</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>45.29285</t>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>125.8145</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>46.02637</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DEV-6331568977-02</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>肇东市传输设备02</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>10.100.0.12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>MR6331568977</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>125.8145</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>46.02637</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DEV-6332406998-01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>兰西县传输设备01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>绥化</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>10.101.0.11</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>MR6332406998</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>CUST-007</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>126.2076</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>46.31811</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DEV-6341507561-01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>铁锋区传输设备01</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>10.102.0.11</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>MR6341507561</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>124.24011</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>47.29106</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DEV-6343642415-01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>昂昂溪区传输设备01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>10.103.0.11</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>MR6343642415</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>123.91449</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>47.14167</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DEV-6343642415-02</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>昂昂溪区传输设备02</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>10.103.0.12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>MR6343642415</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>123.91449</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>47.14167</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DEV-6350394662-01</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>梅里斯达斡尔族区传输设备01</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>齐齐哈尔</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>10.104.0.11</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>MR6350394662</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>CUST-003</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>123.82111</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>47.54548</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DEV-6352034081-01</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>杜尔伯特蒙古族自治县 ᠳᠥᠷᠪᠡᠳ ᠮᠣᠩᠭᠣᠯ ᠥᠪᠡᠷᠲᠡᠭᠡᠨ ᠵᠠᠰᠠᠬᠤ ᠰᠢᠶᠠᠨ传输设备01</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>10.105.0.11</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>MR6352034081</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>124.2244</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>46.52319</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DEV-6352421319-01</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>让胡路区传输设备01</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>10.106.0.11</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>MR6352421319</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>124.78911</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>46.73127</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DEV-6352421319-02</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>让胡路区传输设备02</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>10.106.0.12</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>MR6352421319</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>124.78911</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>46.73127</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DEV-6353763804-01</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>萨尔图区传输设备01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>10.107.0.11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>MR6353763804</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>125.0578</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>46.70944</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DEV-6355869234-01</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>肇源县传输设备01</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>10.108.0.11</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>MR6355869234</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>124.83788</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>45.61143</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DEV-6356225091-01</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>肇州县传输设备01</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>10.109.0.11</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>MR6356225091</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>125.28703</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>45.85095</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DEV-6356225091-02</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>肇州县传输设备02</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>大庆</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>10.109.0.12</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>MR6356225091</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>CUST-004</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>125.28703</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>45.85095</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DEV-6358882012-01</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>平房区传输设备01</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>10.110.0.11</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>MR6358882012</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>CUST-001</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>126.66628</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>45.58461</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DEV-6359892789-01</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>尚志市传输设备01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>10.111.0.11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>MR6359892789</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>128.31581</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>44.9802</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DEV-6373436326-01</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>海林市传输设备01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>10.112.0.11</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>MR6373436326</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>129.25701</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>44.86197</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DEV-6373436326-02</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>海林市传输设备02</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>10.112.0.12</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>MR6373436326</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>129.25701</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>44.86197</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DEV-6375398861-01</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>阳明区传输设备01</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>10.113.0.11</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>MR6375398861</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>129.8576</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>44.66376</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DEV-6375764149-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>穆棱市传输设备01</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>牡丹江</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>10.114.0.11</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>MR6375764149</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>130.37264</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>44.53311</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DEV-6376504260-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>麻山区传输设备01</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>10.115.0.11</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>MR6376504260</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>130.54913</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>45.21185</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DEV-6376504260-02</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>麻山区传输设备02</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>10.115.0.12</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>MR6376504260</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>130.54913</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>45.21185</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>DEV-6377319195-01</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>恒山区传输设备01</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>鸡西</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>10.116.0.11</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>MR6377319195</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>CUST-005</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>130.9288</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>45.16601</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DEV-6380056508-01</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>岭东区传输设备01</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>双鸭山</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>10.117.0.11</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>MR6380056508</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>131.18355</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>46.4834</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DEV-6380925564-01</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>集贤县传输设备01</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>双鸭山</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>10.118.0.11</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>MR6380925564</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>131.17937</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>46.79831</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DEV-6380925564-02</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>集贤县传输设备02</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>双鸭山</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>10.118.0.12</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>MR6380925564</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>131.17937</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>46.79831</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>DEV-6385641267-01</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>郊区传输设备01</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>佳木斯</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>10.119.0.11</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>MR6385641267</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>CUST-006</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>130.2681</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>46.77753</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>DEV-6395573965-01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>勃利县传输设备01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>七台河</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>10.120.0.11</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>MR6395573965</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>RING-JM</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>IGP-ISIS-02</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>CUST-012</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>130.48783</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>45.81668</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>DEV-678337697-01</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>加格达奇区传输设备01</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>中兴</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ZXMP M920</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>10.121.0.11</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>MR678337697</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>124.13165</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>50.40579</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>DEV-678337697-02</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>加格达奇区传输设备02</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>10.121.0.12</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>MR678337697</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>124.13165</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>50.40579</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DEV-678337697-03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>加格达奇区传输设备03</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>OptiX OSN 9800</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>10.121.0.13</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>MR678337697</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>124.13165</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>50.40579</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>DEV-962010355-01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>塔河县-2传输设备01</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>加格达奇</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>烽火</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>CiTRANS 660</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>10.122.0.11</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>MR962010355</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>RING-HDQ</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>IGP-OSPF-01</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>CUST-010</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>124.70199</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>52.33318</t>
         </is>
       </c>
     </row>
